--- a/data/google_news_dedup_29_0426_UTC_past2d.xlsx
+++ b/data/google_news_dedup_29_0426_UTC_past2d.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,22 +600,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gros and Amazon grocery delivery service in Rome: Fruit, vegetables - Hortidaily</t>
+          <t>Who can get Amazon drone delivery in San Antonio? What we know - MSN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Gros and Amazon grocery delivery service in Rome: Fruit, vegetables - Hortidaily</t>
+          <t>Who can get Amazon drone delivery in San Antonio? What we know - MSN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 12:04:09 GMT</t>
+          <t>Wed, 29 Apr 2026 07:38:13 GMT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOWFRWSDg3MGVXQzNNcG5sX2M2Ymc0dm1FQkJHbmZKN0J4SndlWE5aM2llWUxjWGcxOTJ6V1RWS1U1RGsyaU5ScXlHNDNPVDY2NHQwclhIRlUzalhUYkxKR2dON21hX0k5YlJQa2NkSFFwY1d6RW9uR0t5bl83SXZ6S2wxdVE4SVhmWTVfRnRGTWttQlJTMDl2Ty1pLVBtUklLNm0yWlJSaHpYdENNS1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gJBVV95cUxNcUVrQV9TUDZKTDdzVEhhVWNrcFBacUJueWhxd2t1OXZpZ2cyT3hNNzg1bHV1RkRIRmtvN0tzUjN1enhtMkswWGNMdU9Wd1JpRGJMSkx0ZVp3eS1yZDd1RW03dGR2c3NKRWhFQ01sWS1WYTNNYk5JblczaE9xZVVUWlVKY1RueTBwVlB0cWhTb2dtbktwWjFCNXR4VUYzQVFtZ3NTT3hzU25pZW1hUVRRWEdRaEFFbmViSTlXeWNUUkVlcjBFcEhXSC1sMUc4UlA2WmIwT09xZnUxUXMtODFqWDdPbGQ1b3FNM2xzMERSenc5dXhnZlBzQ095a3Nnd3p1VUswc2U0RWVCNjZvdWtXb2dBLWhBSHBLd0lnbE9jandEWDhZTEYzX2xXajJYRHVyeHBscHBpZGlhRG1fQUtreG5xUk5rRXBfYXkwYTJUSTdKUkZ1VllDYnYtM0ctSFdLdWYxRERxb1RKZw?oc=5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46141.50288194444</v>
+        <v>46141.31820601852</v>
       </c>
     </row>
     <row r="5">
@@ -655,22 +655,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Who can get Amazon drone delivery in San Antonio? What we know - MSN</t>
+          <t>Amazon is expanding faster shipping with new 1-hour and 3-hour delivery options - MSN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Who can get Amazon drone delivery in San Antonio? What we know - MSN</t>
+          <t>Amazon is expanding faster shipping with new 1-hour and 3-hour delivery options - MSN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:38:13 GMT</t>
+          <t>Wed, 29 Apr 2026 12:14:50 GMT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gJBVV95cUxNcUVrQV9TUDZKTDdzVEhhVWNrcFBacUJueWhxd2t1OXZpZ2cyT3hNNzg1bHV1RkRIRmtvN0tzUjN1enhtMkswWGNMdU9Wd1JpRGJMSkx0ZVp3eS1yZDd1RW03dGR2c3NKRWhFQ01sWS1WYTNNYk5JblczaE9xZVVUWlVKY1RueTBwVlB0cWhTb2dtbktwWjFCNXR4VUYzQVFtZ3NTT3hzU25pZW1hUVRRWEdRaEFFbmViSTlXeWNUUkVlcjBFcEhXSC1sMUc4UlA2WmIwT09xZnUxUXMtODFqWDdPbGQ1b3FNM2xzMERSenc5dXhnZlBzQ095a3Nnd3p1VUswc2U0RWVCNjZvdWtXb2dBLWhBSHBLd0lnbE9jandEWDhZTEYzX2xXajJYRHVyeHBscHBpZGlhRG1fQUtreG5xUk5rRXBfYXkwYTJUSTdKUkZ1VllDYnYtM0ctSFdLdWYxRERxb1RKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipANBVV95cUxPZW1hbE9CZGhEQmI1Rl9RdllkSjBlZUpla192b0Ruc0xCMVEtcVV2bE9uZkE4NEFrYnZLeHNrSzBwbnJZSmlHaUNhdFNvakdOTVYyYk1tYjluVWswVU0tbnhYN3RjaVRIS3RUNml5WWxMeU9uUE1Tdk9VVzB0MDJ4bnVLOVV1UXlvemcwazlic3RkS0FuYmxZSml1ZENUTVRfMzBzWFJLT1E2VDZjVmFjc09ZbmNWbFdBa2xzbWVDZkxOVWFNQTdfb3pXWnQyX1lnWFFBRkY1Z0RxVkVINWZQSUNhQUFxUlgzd1YwOEF5MmpsdXZvcDh0QS12dnFHMjZENXNMUmpNZjZTNlliVnNTUFBna3BoQmFib2Jadk53bDZjY0p4NG9CX05SMUIwR3NteF9wd2FSS2ctc01wclpEMTlMb214T3k0RGNzYzlsZmNtd2c4RW43bFRrLVpUQXRNakdvY0ZGNFMwZjRhNHBoR25YZFZGXzdQeUg1eHB2OTZ0dUxfSXc4dVp1R29BdFRNbER0bGMyNlE2RXItOFNOdzlsa3M?oc=5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -694,38 +694,38 @@
         </is>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46141.31820601852</v>
+        <v>46141.51030092593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amazon is expanding faster shipping with new 1-hour and 3-hour delivery options - MSN</t>
+          <t>Ex-president van Zuid-Korea krijgt 7 jaar cel voor verzet tegen arrestatie - Nieuwsblad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Amazon is expanding faster shipping with new 1-hour and 3-hour delivery options - MSN</t>
+          <t>Ex-president of South Korea gets 7 years in prison for resisting arrest - Nieuwsblad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 12:14:50 GMT</t>
+          <t>Wed, 29 Apr 2026 10:37:44 GMT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipANBVV95cUxPZW1hbE9CZGhEQmI1Rl9RdllkSjBlZUpla192b0Ruc0xCMVEtcVV2bE9uZkE4NEFrYnZLeHNrSzBwbnJZSmlHaUNhdFNvakdOTVYyYk1tYjluVWswVU0tbnhYN3RjaVRIS3RUNml5WWxMeU9uUE1Tdk9VVzB0MDJ4bnVLOVV1UXlvemcwazlic3RkS0FuYmxZSml1ZENUTVRfMzBzWFJLT1E2VDZjVmFjc09ZbmNWbFdBa2xzbWVDZkxOVWFNQTdfb3pXWnQyX1lnWFFBRkY1Z0RxVkVINWZQSUNhQUFxUlgzd1YwOEF5MmpsdXZvcDh0QS12dnFHMjZENXNMUmpNZjZTNlliVnNTUFBna3BoQmFib2Jadk53bDZjY0p4NG9CX05SMUIwR3NteF9wd2FSS2ctc01wclpEMTlMb214T3k0RGNzYzlsZmNtd2c4RW43bFRrLVpUQXRNakdvY0ZGNFMwZjRhNHBoR25YZFZGXzdQeUg1eHB2OTZ0dUxfSXc4dVp1R29BdFRNbER0bGMyNlE2RXItOFNOdzlsa3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNEVmWmR2V1c0MUhremREaXhqeW8yVjFRZ0ZjdXBGcFlJRXc4dTdMcFMxOFdCTXloZUJibVVHZU1RN0g2dlpoQ2tvX2tMWkdEUDFEQ01yUGpSS3c4MERhdnA4WTdUUDAtYWdnal8tS2x6LWM5d3BpTXRzSDRydHRwOHpNWTJtN0tSZjgweWNPNWhDR1R3NTh2YkRDdkRIWG56YS0zUUJQZ3c2bkxiQU5ZVlZuM3puQjhMVVpOYXhFa0R6MHg0?oc=5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -735,52 +735,52 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46141.51030092593</v>
+        <v>46141.44287037037</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amazon unveils AI tools to reshape jobs and supply chains - dqindia.com</t>
+          <t>Hungary's Magyar visits Brussels seeking to unblock EU billions - Nonstop Local News</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Amazon unveils AI tools to reshape jobs and supply chains - dqindia.com</t>
+          <t>Hungary's Magyar visits Brussels seeking to unblock EU billions - Nonstop Local News</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:25:21 GMT</t>
+          <t>Wed, 29 Apr 2026 09:32:15 GMT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOUnFmeEl1emRTem1lWVY1Q3ZkMUxvZEkzalAxVlNqNDRXMEJjbEZKVkprSFlpYWs2RzlWcDRJaUZJREhIMXpxWW1BcWdWZGI3NUZNS1ktOU1faENiaVZuRnUwcWhOY2pTMDlYWkZGWjZ2ZTYyTXlLWnZQTk42VEprYzVaalplbE91cnRya3BVVFBoY05xWlBVYlh3Z9IBmwFBVV95cUxOUnFmeEl1emRTem1lWVY1Q3ZkMUxvZEkzalAxVlNqNDRXMEJjbEZKVkprSFlpYWs2RzlWcDRJaUZJREhIMXpxWW1BcWdWZGI3NUZNS1ktOU1faENiaVZuRnUwcWhOY2pTMDlYWkZGWjZ2ZTYyTXlLWnZQTk42VEprYzVaalplbE91cnRya3BVVFBoY05xWlBVYlh3Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOMlB6Y2pFTVNoRXdyNGxPdTVhdV9CZGdSeGxwaGx3aVVVaWcwNE5OZzV3cmVLeG9IWVVLQi1LSm9kTWdRQVA4ejROZGxySVF6QzAtSy1VbHhmWWgwcGJPUnN3TEZlcFRyMk9ITEJMaFdIckl1ek1VRmVtY0NqU0xnT1psblBuU19HY2NsZ1dpUy1FVDBGOTRsSVJnbmxDNVYtOEdySHJNOW5ZYThLVkw2SndGblVEa2hUSTB0UlJ5YnYzQXlRWWFDWVpUWEtNYkR5cExvOXZyV2UycjU0UHpYbW15MA?oc=5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -795,47 +795,47 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46141.30927083334</v>
+        <v>46141.39739583333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ex-president van Zuid-Korea krijgt 7 jaar cel voor verzet tegen arrestatie - Nieuwsblad</t>
+          <t>EU plans crackdown on heavy fireworks after NL appeal - DutchNews.nl</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ex-president of South Korea gets 7 years in prison for resisting arrest - Nieuwsblad</t>
+          <t>EU plans crackdown on heavy fireworks after NL appeal - DutchNews.nl</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:37:44 GMT</t>
+          <t>Wed, 29 Apr 2026 12:49:57 GMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNEVmWmR2V1c0MUhremREaXhqeW8yVjFRZ0ZjdXBGcFlJRXc4dTdMcFMxOFdCTXloZUJibVVHZU1RN0g2dlpoQ2tvX2tMWkdEUDFEQ01yUGpSS3c4MERhdnA4WTdUUDAtYWdnal8tS2x6LWM5d3BpTXRzSDRydHRwOHpNWTJtN0tSZjgweWNPNWhDR1R3NTh2YkRDdkRIWG56YS0zUUJQZ3c2bkxiQU5ZVlZuM3puQjhMVVpOYXhFa0R6MHg0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOZ29yY0c5V0hkTW9obDNRdFV0aU5rSE9nbWQ2Yy05QngzRHR1QkxZMERtN1B6MHRyYzR4Y2lBSmk1eENIVDktNjEza2s4Xy1MV2paVlJmd21ibHBZUk9fLXZ4TDRnbEEyc05lTmtuMXdOU2ZwMTdlSmtLa05RTjNUcTJkbzc0c2RpeVpNR0ZZYXU?oc=5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -855,11 +855,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46141.44287037037</v>
+        <v>46141.5346875</v>
       </c>
     </row>
     <row r="9">
@@ -875,22 +875,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hungary's Magyar visits Brussels seeking to unblock EU billions - Nonstop Local News</t>
+          <t>‘Total failure’: Leading economists tear into German federal budget - Brussels Signal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hungary's Magyar visits Brussels seeking to unblock EU billions - Nonstop Local News</t>
+          <t>‘Total failure’: Leading economists tear into German federal budget - Brussels Signal</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 09:32:15 GMT</t>
+          <t>Wed, 29 Apr 2026 10:14:10 GMT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOMlB6Y2pFTVNoRXdyNGxPdTVhdV9CZGdSeGxwaGx3aVVVaWcwNE5OZzV3cmVLeG9IWVVLQi1LSm9kTWdRQVA4ejROZGxySVF6QzAtSy1VbHhmWWgwcGJPUnN3TEZlcFRyMk9ITEJMaFdIckl1ek1VRmVtY0NqU0xnT1psblBuU19HY2NsZ1dpUy1FVDBGOTRsSVJnbmxDNVYtOEdySHJNOW5ZYThLVkw2SndGblVEa2hUSTB0UlJ5YnYzQXlRWWFDWVpUWEtNYkR5cExvOXZyV2UycjU0UHpYbW15MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNQ3pQbnZaVFM2cnN6ZzZpMlk5WHlVZENiSkxJZmx5NzFWb2lkZHBIYVZGbzlWVlpISUpjQmFpSHJLTldrVGhBZ1RMQUZoSFJ4UU13OHczNmdxLThXRVJDOXZvSlVabDFSRER4bmVpQjYyWW8xdVl6MnNmRTFNdGRSTVNxTVk0Y3Zldm8wWEowTXRfZ0psNGdvVF90M0FnWGJw?oc=5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46141.39739583333</v>
+        <v>46141.42650462963</v>
       </c>
     </row>
     <row r="10">
@@ -930,22 +930,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EU plans crackdown on heavy fireworks after NL appeal - DutchNews.nl</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EU plans crackdown on heavy fireworks after NL appeal - DutchNews.nl</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 12:49:57 GMT</t>
+          <t>Wed, 29 Apr 2026 13:05:46 GMT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOZ29yY0c5V0hkTW9obDNRdFV0aU5rSE9nbWQ2Yy05QngzRHR1QkxZMERtN1B6MHRyYzR4Y2lBSmk1eENIVDktNjEza2s4Xy1MV2paVlJmd21ibHBZUk9fLXZ4TDRnbEEyc05lTmtuMXdOU2ZwMTdlSmtLa05RTjNUcTJkbzc0c2RpeVpNR0ZZYXU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQeW92M1I2ZGttX1FtVWRBaHRyZUtib3lhY0x5OUU4ZUsyUGxEc0RReW1PVFlFUzhsWmJGcEd0d0RaYXlvd0RYXzZVVVdfa0EzNlhzVXc3TE82OWxkS1ZwNDE5d0NBUy1KSGxkLV9EZ1NvZ0VpdnM0YnhWSkN6MHVnWDJPbjduNTNfajlCWW1ibURwTkkxdi1kV01scXBuVEd1cnQ3LWE0YUt3Zjd1ckRQeFFzcEdXdw?oc=5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46141.5346875</v>
+        <v>46141.5456712963</v>
       </c>
     </row>
     <row r="11">
@@ -985,22 +985,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>‘Total failure’: Leading economists tear into German federal budget - Brussels Signal</t>
+          <t>Brussels opens proceedings against Portugal for failing to carry out a road assessment of the main national roads - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>‘Total failure’: Leading economists tear into German federal budget - Brussels Signal</t>
+          <t>Brussels opens proceedings against Portugal for failing to carry out a road assessment of the main national roads - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:14:10 GMT</t>
+          <t>Wed, 29 Apr 2026 13:03:47 GMT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNQ3pQbnZaVFM2cnN6ZzZpMlk5WHlVZENiSkxJZmx5NzFWb2lkZHBIYVZGbzlWVlpISUpjQmFpSHJLTldrVGhBZ1RMQUZoSFJ4UU13OHczNmdxLThXRVJDOXZvSlVabDFSRER4bmVpQjYyWW8xdVl6MnNmRTFNdGRSTVNxTVk0Y3Zldm8wWEowTXRfZ0psNGdvVF90M0FnWGJw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOZXdHaHRaWDZsTWl5WGxHd0hteFdkYXRXYkQ5OHZOWGFKUGlLMVdPcm16VlNLQkxzNEhDZktIUjlqdExUejZyT0FZQTlJa3NMZWtWVTF6WnhfaWlhTVMzVXJEUEJ0dEdsR3FnU3gwX3F3Z3VwS0RkbDdhS19CUzdYQ1BVMm5meDlHaDBvMThOcXFvT2NKODNvY01vZXJVc3RnN0x5bU9rSXFrU2pCYzdLODNYaFdqYzRESTBXZVVaUjhrT1NmNUtXVEF6Z0oxY1A3VUJrY0IzaWZCTWwyS3ZldVBtYXNKYVE?oc=5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,38 +1024,38 @@
         </is>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46141.42650462963</v>
+        <v>46141.54429398148</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
+          <t>Ponts de mai : explosion des réservations vers Aix et Marseille, le week-end du 8 mai bat des records ! - Maritima</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
+          <t>May bridges: explosion of reservations to Aix and Marseille, the weekend of May 8 breaks records! -Maritima</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 13:05:46 GMT</t>
+          <t>Wed, 29 Apr 2026 10:13:00 GMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQeW92M1I2ZGttX1FtVWRBaHRyZUtib3lhY0x5OUU4ZUsyUGxEc0RReW1PVFlFUzhsWmJGcEd0d0RaYXlvd0RYXzZVVVdfa0EzNlhzVXc3TE82OWxkS1ZwNDE5d0NBUy1KSGxkLV9EZ1NvZ0VpdnM0YnhWSkN6MHVnWDJPbjduNTNfajlCWW1ibURwTkkxdi1kV01scXBuVEd1cnQ3LWE0YUt3Zjd1ckRQeFFzcEdXdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOdmtjTnZJeVR5aEVjUjNhejhEcklNNDQ4b0tzR2JyM2cwZlVIbV83UWNaWm02VkVxbk9KZml5NnZtc1NhVkRuci1FVi1CRS1RbVBiVWtXR1h1SVItU0pDelJnRTRXMEpfX3ZJM1hzTWliZm9hTnA2MHRsMUtmLXRZMWpFa0ZaRUNjaEgxbTQ3ZHd6aTVZaXJLLXhKWVZpd2g0R2w3Yng1UHFWTFQ3Q3BGVkFDMnkySDl6SC05TFZRZlJzUExnM0JxZ1duX1ZuSHZKTWduRFJFa2F6NTE5SjF4M3dsU1ZGZElfX25GZU1iVlRJQQ?oc=5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1075,42 +1075,42 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46141.5456712963</v>
+        <v>46141.42569444444</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brussels opens proceedings against Portugal for failing to carry out a road assessment of the main national roads - lnginnorthernbc.ca</t>
+          <t>Patrick Bruel : « Il faut entendre les deux », le malaise d'Aurore Bergé face aux 18 accusatrices - Legossip.net</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Brussels opens proceedings against Portugal for failing to carry out a road assessment of the main national roads - lnginnorthernbc.ca</t>
+          <t>Patrick Bruel: “You have to hear both”, Aurore Bergé’s discomfort in the face of the 18 accusers - Legossip.net</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 13:03:47 GMT</t>
+          <t>Wed, 29 Apr 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOZXdHaHRaWDZsTWl5WGxHd0hteFdkYXRXYkQ5OHZOWGFKUGlLMVdPcm16VlNLQkxzNEhDZktIUjlqdExUejZyT0FZQTlJa3NMZWtWVTF6WnhfaWlhTVMzVXJEUEJ0dEdsR3FnU3gwX3F3Z3VwS0RkbDdhS19CUzdYQ1BVMm5meDlHaDBvMThOcXFvT2NKODNvY01vZXJVc3RnN0x5bU9rSXFrU2pCYzdLODNYaFdqYzRESTBXZVVaUjhrT1NmNUtXVEF6Z0oxY1A3VUJrY0IzaWZCTWwyS3ZldVBtYXNKYVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPSWhxTGVBQ0lHb05xc3JTTW9ZbjJmYkQxNnVQaktpNUNhWF9EMnpucUlPYTBGcjlwXzczTko3andjT0gtc1VkVUozRDhLU2hrSTYzeEdkNjVvcm9HRWUtUzR5MEZwalppRmhXVl9JbVJIRnc1NmFWMnhYcDdvQ0luM210TGdPRVJRRXliSVJPQmdHcFNzbmVpOWNEeUxmcS1jV1JGb2xvbDMxZ3Na?oc=5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1130,42 +1130,42 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46141.54429398148</v>
+        <v>46141.33333333334</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>Local Town Maasmechelen French</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Patrick Bruel désormais visé par une enquête en Belgique - MSN</t>
+          <t>Un individu impliqué dans une bagarre à Maasmechelen placé sous surveillance électronique - DHnet</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Patrick Bruel now targeted by investigation in Belgium - MSN</t>
+          <t>Individual involved in fight in Maasmechelen placed under electronic surveillance - DHnet</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:32:36 GMT</t>
+          <t>Wed, 29 Apr 2026 13:46:00 GMT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinANBVV95cUxPRzZCMXdZWEpJWjgybnBQSW0wc19DZmVzTmJiTFJjTkxsMDFPOU5QdGp1QVJnc1VOVXhrNE5LM2JYRUNHRDZfT1JBYkxHdHY0MlpvdWFuZnEtb2tacGdIZUY0OHdNcnpnaEhwUnhERTJHTllGZ1VaZzZhNDRTX1dZTmVZaTVBdUJmZFptQmxCNk5oT0pmTXJtZDdWRFgzbHk1RUtCQ3pIY3JIYkQ1RHplQTlvWjExVEs3U1dtT2hDZ0VmLW5vVG9PbWVpNzd5M19kM19aMEtUQnZFVzhfQTJidEpVUEhESjBpcTZ5Yk9VRkg0YThhSDBoWEtkc0lFVW1Yc0lDd2hpSS1YTHdtSjNlTkRqNFVQVWhyeWpUaUQ0RnpNWm10WEY4QVhRNS1yYlJjd2gzOXBydDBCYno5VGcycFpua1BhZk8xVzJ5eHpIbmc4dmtsNUdCZlVEMDhQc2lXYzgtb3hVb2h1U2wwMFBBenNOa2M1ZkFBVGdrNGpmaF9QeWRhckUxblRMcms5a0pqMEV3TWUyWmw5SUM2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxPV3g3cTJpLUNzb0Q3cXF1X24yMUdtZTBwUExFZ09XWFVVaXgyREdDZDZfYVUtVWNhaWk0eFhLMG05OEE4TS1HYk1BXzZpZkRyMWpaQXRHMjlNZDl4ekNvZ21PTlJlOFhWaGVwM0NKX3NwSTc5aXNCUEVRZXJCZE83VUt6VDlKbWFjUi1HNXJ5MjdxekI0WkhoZXR0bF80ZUloSFM3UnV5NF96dmc4YlVjRjdMa05MVUZMOUpFMzdKX21qSkgxVDM2NTVBVEJSR0lBUDVDQWtwbWRGclN2b25nNWxQQ2p1NGFzSDF0Z0ZHY1NJOF9sMkJZMmprZEU?oc=5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1189,38 +1189,38 @@
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46141.31430555556</v>
+        <v>46141.57361111111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ponts de mai : explosion des réservations vers Aix et Marseille, le week-end du 8 mai bat des records ! - Maritima</t>
+          <t>Mystery as billionaire socialite is found dead inside her cabin on luxurious cruise ship - MSN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>May bridges: explosion of reservations to Aix and Marseille, the weekend of May 8 breaks records! -Maritima</t>
+          <t>Mystery as billionaire socialite is found dead inside her cabin on luxurious cruise ship - MSN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:13:00 GMT</t>
+          <t>Wed, 29 Apr 2026 10:56:02 GMT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOdmtjTnZJeVR5aEVjUjNhejhEcklNNDQ4b0tzR2JyM2cwZlVIbV83UWNaWm02VkVxbk9KZml5NnZtc1NhVkRuci1FVi1CRS1RbVBiVWtXR1h1SVItU0pDelJnRTRXMEpfX3ZJM1hzTWliZm9hTnA2MHRsMUtmLXRZMWpFa0ZaRUNjaEgxbTQ3ZHd6aTVZaXJLLXhKWVZpd2g0R2w3Yng1UHFWTFQ3Q3BGVkFDMnkySDl6SC05TFZRZlJzUExnM0JxZ1duX1ZuSHZKTWduRFJFa2F6NTE5SjF4M3dsU1ZGZElfX25GZU1iVlRJQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwNBVV95cUxOWmdablhpN05fVHljdzQ0SWFfUWtzWmZ3cS1yeHZaNFd5d2ZfYVBSUzluclljdE9ta3p3dkdoUHMwVllRMVJGbktRbDBmRk1YVFRGUGVhWlRGSWNwNDJTSFJyamg3ZmtaWVlTaXlCVF8xYTVrVlZGN2RLU3RRYjlkekd6bENRN2JHOUZXNFNnUnpucW1FQVhVQUxWdFJlZ2VjRV9XSnF6WVJFUFBQTjZBUTc1YTd0M0Q3bXZEb0g2MHhuTFBjei1vUmJNMzN5WWVtZEVaSkZMcEt2cHZGR2ZhWVV0NnBBeVc0Q1M3YUJZY0VOQTQzSlBwWlNLWDAyYzBYWFFkeEdTY2V4NzN2S0Y4TjlLdDU5RjVkamtSTFliLVB2X0tfSjQzOXBsQlZPVElDU3dPQVhaR01jLVg0cmxzRXhMcEw2V1FuYlVmRXp5dDk4eUowVFlSLTRpZkFSZ3JMSmRpRFU2dVBQNEdaTmZoTWpFTklOeDRCeFkzbk5UTWQ2a1UtcUxHMWgzUmM2NWExSGcxY3FHU1pWSTZwRWhVMUIzLVdtRmhQVFBF?oc=5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1230,52 +1230,52 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46141.42569444444</v>
+        <v>46141.4555787037</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Patrick Bruel : « Il faut entendre les deux », le malaise d'Aurore Bergé face aux 18 accusatrices - Legossip.net</t>
+          <t>Roddick and Wertheim share caution around Alcaraz wrist injury : "I don’t think you ever question a player taking the long view with an injury" - Tennisuptodate.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Patrick Bruel: “You have to hear both”, Aurore Bergé’s discomfort in the face of the 18 accusers - Legossip.net</t>
+          <t>Roddick and Wertheim share caution around Alcaraz wrist injury : "I don’t think you ever question a player taking the long view with an injury" - Tennisuptodate.com</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 08:00:00 GMT</t>
+          <t>Wed, 29 Apr 2026 09:33:16 GMT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPSWhxTGVBQ0lHb05xc3JTTW9ZbjJmYkQxNnVQaktpNUNhWF9EMnpucUlPYTBGcjlwXzczTko3andjT0gtc1VkVUozRDhLU2hrSTYzeEdkNjVvcm9HRWUtUzR5MEZwalppRmhXVl9JbVJIRnc1NmFWMnhYcDdvQ0luM210TGdPRVJRRXliSVJPQmdHcFNzbmVpOWNEeUxmcS1jV1JGb2xvbDMxZ3Na?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNNVl6N0kzWGpaUDZDUXlhZW44eTk4RHdiSjB4VmVUVkcyOFJ3SzM1b29hUVg4OWYway1OX3VxTzN2SElKMjhLRXpJSnVkOHB5T0hzRDcwUEVYcm5VYzdpVEhEZE5PTHlaSW13aXhVUlcyZXJkTkdDRDZ0dE9vUktkOElNbDJPVFI0aVJZUXlPSnZiOXRYUy02cWtuYmhybDNGbHdLbzJFOHdyekhOeHFkZ242ZWtIM0dib2hwdWFZeG5tT3VTWVdQZ3BSSDVNdmJGUERaalFBcDBtOEtqalZaYnk1UXlSTEdMUkhadDViUWY5REZQSzgwY2JPY2dtdw?oc=5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1285,52 +1285,52 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46141.33333333334</v>
+        <v>46141.39810185185</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Un individu impliqué dans une bagarre à Maasmechelen placé sous surveillance électronique - DHnet</t>
+          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Individual involved in fight in Maasmechelen placed under electronic surveillance - DHnet</t>
+          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 13:46:00 GMT</t>
+          <t>Wed, 29 Apr 2026 12:20:38 GMT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxPV3g3cTJpLUNzb0Q3cXF1X24yMUdtZTBwUExFZ09XWFVVaXgyREdDZDZfYVUtVWNhaWk0eFhLMG05OEE4TS1HYk1BXzZpZkRyMWpaQXRHMjlNZDl4ekNvZ21PTlJlOFhWaGVwM0NKX3NwSTc5aXNCUEVRZXJCZE83VUt6VDlKbWFjUi1HNXJ5MjdxekI0WkhoZXR0bF80ZUloSFM3UnV5NF96dmc4YlVjRjdMa05MVUZMOUpFMzdKX21qSkgxVDM2NTVBVEJSR0lBUDVDQWtwbWRGclN2b25nNWxQQ2p1NGFzSDF0Z0ZHY1NJOF9sMkJZMmprZEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gJBVV95cUxQY01iZmJiZ1g0ZnoxcnZzUG5lUURqd1pSMFhkX214bFB1SFRJZElmTHdjUy1FNnpxbkVUVk5JNlY5NUlJRVRmS1E2TnkyaktsR2FDR3FEczBHRVViaUFUWDNMNlAxakpMNnRZeXQ0bG4zd1NRN2tGWGpQOWFybFlDeVNGUFBiS2FiSWFOalBGcFVLaDMyR2NIZDNKcTJBZ1AtTzdnQ2JRbUg2SUNqVGd5ekM0d2RKUmRlX2R0Z2daUzNDQ1FQX3Znck9VcUJkSHVOR2t4d0VFVzZLR2hWYnQyNnNSMVZhQWxvdVVYQ3ExeVBGMHhOSW4zYkZCSFBfdG9SdGU5WVQzMHEzLXJDRnNhOUZqYlU2TGNTS19KM2pORHBJclBSdzZNWUtxZURZeVRxb1c0ckU5cExWV1VUa0ExMVlnRUdnOUFodlJjWElpTzlmckNFbERES1dBelluZw?oc=5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1340,21 +1340,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46141.57361111111</v>
+        <v>46141.51432870371</v>
       </c>
     </row>
     <row r="18">
@@ -1370,22 +1370,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Roddick and Wertheim share caution around Alcaraz wrist injury : "I don’t think you ever question a player taking the long view with an injury" - Tennisuptodate.com</t>
+          <t>Miami top stories: Women-owned businesses, philanthropist’s death, Charlamagne - Miami Herald</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Roddick and Wertheim share caution around Alcaraz wrist injury : "I don’t think you ever question a player taking the long view with an injury" - Tennisuptodate.com</t>
+          <t>Miami top stories: Women-owned businesses, philanthropist’s death, Charlamagne - Miami Herald</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 09:33:16 GMT</t>
+          <t>Wed, 29 Apr 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNNVl6N0kzWGpaUDZDUXlhZW44eTk4RHdiSjB4VmVUVkcyOFJ3SzM1b29hUVg4OWYway1OX3VxTzN2SElKMjhLRXpJSnVkOHB5T0hzRDcwUEVYcm5VYzdpVEhEZE5PTHlaSW13aXhVUlcyZXJkTkdDRDZ0dE9vUktkOElNbDJPVFI0aVJZUXlPSnZiOXRYUy02cWtuYmhybDNGbHdLbzJFOHdyekhOeHFkZ242ZWtIM0dib2hwdWFZeG5tT3VTWVdQZ3BSSDVNdmJGUERaalFBcDBtOEtqalZaYnk1UXlSTEdMUkhadDViUWY5REZQSzgwY2JPY2dtdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQa0FxVGR6Zkxyd2IxX2cyV3N4WnlRSGxTVmZjbktUOTE4NkwwNHJPNVVBNndjZ0dqTU9rb3phWkhrNFVrdHpGXzBORzdJVFFacU9Lem5YRXN2YlNOTFN1c2VSVjM3VTJUTzlWNFlFaXY1ZzVGZF9MdmVrbmNWc1RfQmpnZDdlakVr0gGIAUFVX3lxTE42aW1SaTV3aUtTRnFMYi1mVmZMR1hGN1dvZUxGdGNfRmVwT0gyel9oNm5Kek9LT19tOS1aeERhS05XaE5EVi1HQlVyYVRfVEQ4anBqeUQ0NUdKS2lZQUNxbHFnWlFtOV9qRnltMlFjUm1TdzZhR2NjUkhDWDRveTZFVDNBLTM3REM?oc=5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46141.39810185185</v>
+        <v>46141.375</v>
       </c>
     </row>
     <row r="19">
@@ -1425,22 +1425,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
+          <t>Rafael Jodar surpasses Big 3, Sinner and Alcaraz with historic start to ATP career - Tennis Tonic</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
+          <t>Rafael Jodar surpasses Big 3, Sinner and Alcaraz with historic start to ATP career - Tennis Tonic</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 12:20:38 GMT</t>
+          <t>Wed, 29 Apr 2026 07:29:30 GMT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gJBVV95cUxQY01iZmJiZ1g0ZnoxcnZzUG5lUURqd1pSMFhkX214bFB1SFRJZElmTHdjUy1FNnpxbkVUVk5JNlY5NUlJRVRmS1E2TnkyaktsR2FDR3FEczBHRVViaUFUWDNMNlAxakpMNnRZeXQ0bG4zd1NRN2tGWGpQOWFybFlDeVNGUFBiS2FiSWFOalBGcFVLaDMyR2NIZDNKcTJBZ1AtTzdnQ2JRbUg2SUNqVGd5ekM0d2RKUmRlX2R0Z2daUzNDQ1FQX3Znck9VcUJkSHVOR2t4d0VFVzZLR2hWYnQyNnNSMVZhQWxvdVVYQ3ExeVBGMHhOSW4zYkZCSFBfdG9SdGU5WVQzMHEzLXJDRnNhOUZqYlU2TGNTS19KM2pORHBJclBSdzZNWUtxZURZeVRxb1c0ckU5cExWV1VUa0ExMVlnRUdnOUFodlJjWElpTzlmckNFbERES1dBelluZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOUUEycjNGSThwMW5EVGFHTkotMVdUYjNwY0xiWWJzU19tQmVoX0k4R195QVlaUEltVDFSN2NISXp0Ynp6TWZpTHdWeUtzWHRHTFBpTTdVOVhfZHFfTzlJdWlxTFktcTNqRVMydmhNcWJhWEtFMVBGZ1cwT3NfUFptemp0UjRMM19nc1gycUlHajZaV1lRNUZmSXpObWNBRV80QXBBT0RRSkp3c0RfOUlGMXA2VFdObXJmLXo1TWFKRi10eVk?oc=5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1464,38 +1464,38 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46141.51432870371</v>
+        <v>46141.31215277778</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>Village Bicester Kildare</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Bicester Village" OR "Kildare Village" OR "Bicester outlet" OR "Kildare outlet")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Miami top stories: Women-owned businesses, philanthropist’s death, Charlamagne - Miami Herald</t>
+          <t>Why coachloads of Chinese tourists are flocking to your favourite beauty spot - MSN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Miami top stories: Women-owned businesses, philanthropist’s death, Charlamagne - Miami Herald</t>
+          <t>Why coachloads of Chinese tourists are flocking to your favourite beauty spot - MSN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 09:00:00 GMT</t>
+          <t>Wed, 29 Apr 2026 08:43:31 GMT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQa0FxVGR6Zkxyd2IxX2cyV3N4WnlRSGxTVmZjbktUOTE4NkwwNHJPNVVBNndjZ0dqTU9rb3phWkhrNFVrdHpGXzBORzdJVFFacU9Lem5YRXN2YlNOTFN1c2VSVjM3VTJUTzlWNFlFaXY1ZzVGZF9MdmVrbmNWc1RfQmpnZDdlakVr0gGIAUFVX3lxTE42aW1SaTV3aUtTRnFMYi1mVmZMR1hGN1dvZUxGdGNfRmVwT0gyel9oNm5Kek9LT19tOS1aeERhS05XaE5EVi1HQlVyYVRfVEQ4anBqeUQ0NUdKS2lZQUNxbHFnWlFtOV9qRnltMlFjUm1TdzZhR2NjUkhDWDRveTZFVDNBLTM3REM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNQmZMOFBsemJmaDBsSTBkMXByTUNENW0yU1JDVGQ1dC1VREhyU1lXdGpOS1VmdDFWVXJjQjdmSkZQN3cxazRuS2M4bkl5N2hZLWZ1MEkySXVhT2tZS1BiNXZXbmdvdzVtRHNvdEN5dTZVQU9PVXNBaXdCMnl1WGExNnllLU9lbFNMbnRpSDQzSFg0TVhsMlFJQVVlbTRpN1JZTlotRVpYa2d0UnRLVXZfYTB3WXRyUGs0V0t1NTlFX2ZiVDdwSlN6ZXBPYm5uX3h4eG84UHVYc2FFdGJtdmhvNFpIRmxkblNjYjNMMEhJbV9SUG5zUHlFeUwwM1VuTWJtT3hzQ0d3?oc=5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1519,38 +1519,38 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46141.375</v>
+        <v>46141.36355324074</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rafael Jodar surpasses Big 3, Sinner and Alcaraz with historic start to ATP career - Tennis Tonic</t>
+          <t>Footage appears to show person being arrested in London after Golders Green stabbing - Sky News</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rafael Jodar surpasses Big 3, Sinner and Alcaraz with historic start to ATP career - Tennis Tonic</t>
+          <t>Footage appears to show person being arrested in London after Golders Green stabbing - Sky News</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:29:30 GMT</t>
+          <t>Wed, 29 Apr 2026 11:59:39 GMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOUUEycjNGSThwMW5EVGFHTkotMVdUYjNwY0xiWWJzU19tQmVoX0k4R195QVlaUEltVDFSN2NISXp0Ynp6TWZpTHdWeUtzWHRHTFBpTTdVOVhfZHFfTzlJdWlxTFktcTNqRVMydmhNcWJhWEtFMVBGZ1cwT3NfUFptemp0UjRMM19nc1gycUlHajZaV1lRNUZmSXpObWNBRV80QXBBT0RRSkp3c0RfOUlGMXA2VFdObXJmLXo1TWFKRi10eVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPVFlwcFBZallGZzJVVjVmeWxtMUt4cE44SkxKYTFfbUlOZUQyUG9mSTVmUmlzZm5vVXBWSG9USDJFb1J0LVJScjdnRnJMb2FSMmNLMnpXbnJBMzJQWlJRaHBXbXZMZEJUMzJaVnBSaGJ4eEx2Nm5Od1VGMVhETUxreFJocTRQTlhrdWhTUlRKZXNuR3lXUlV5aTY0c2lNUEVUZ1dkMEg0SFBPREN0b1IzOFplQ3NJanN4MDI1Tw?oc=5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1574,38 +1574,38 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46141.31215277778</v>
+        <v>46141.49975694445</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Local Town Ingolstadt German</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Polizei- und Feuerwehrmeldungen am 29.04.2026 aus Bayern - Newsflash24</t>
+          <t>Fourth man arrested after 'stabbing' at Oxford park - Oxford Mail</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Police and fire brigade reports from Bavaria on April 29, 2026 - Newsflash24</t>
+          <t>Fourth man arrested after 'stabbing' at Oxford park - Oxford Mail</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 06:49:46 GMT</t>
+          <t>Wed, 29 Apr 2026 10:58:00 GMT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQUmV5UC1NZV92Y0VpLTlWMFFjYW42aHdscXVTS0daeGN3c3h5cWJUWFJPckRWNWVaR0Q5OWNUY0lORkJLWWZueDgwZjZBOURCMlNyYkVMbWY4a0hvUWpKWHhabHFtZ1hkZTk5Rmp6T3pGMHhpTHc2MnV1Ny1hdDVJMDZ0Z3EyYzhwcndINnRXMVhXcE8zX3FiZ2lORS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPaUI1MW81X2g2ZDEyeHpzajNkOE1WV0c4Vk10dnRFak1ENWNDRFFXWDVMdUI5VTI3TTI5S29fbHZCV01jSVNUa0xhZmladzFfcWt3VS04V2JSM2RHSjExRjRmQ2FOWnp2dkRDcU41LVk0d3MyMHZYU1hSRm4zOUo0YlJGWlB5aVNhUEx0TDM0V2F6V0Zta2c?oc=5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1615,52 +1615,52 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46141.28456018519</v>
+        <v>46141.45694444444</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Village Bicester Kildare</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Bicester Village" OR "Kildare Village" OR "Bicester outlet" OR "Kildare outlet")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Why coachloads of Chinese tourists are flocking to your favourite beauty spot - MSN</t>
+          <t>Appeal launched after violent park altercation leaves man stabbed - London Now</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Why coachloads of Chinese tourists are flocking to your favourite beauty spot - MSN</t>
+          <t>Appeal launched after violent park altercation leaves man stabbed - London Now</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 08:43:31 GMT</t>
+          <t>Wed, 29 Apr 2026 10:52:24 GMT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNQmZMOFBsemJmaDBsSTBkMXByTUNENW0yU1JDVGQ1dC1VREhyU1lXdGpOS1VmdDFWVXJjQjdmSkZQN3cxazRuS2M4bkl5N2hZLWZ1MEkySXVhT2tZS1BiNXZXbmdvdzVtRHNvdEN5dTZVQU9PVXNBaXdCMnl1WGExNnllLU9lbFNMbnRpSDQzSFg0TVhsMlFJQVVlbTRpN1JZTlotRVpYa2d0UnRLVXZfYTB3WXRyUGs0V0t1NTlFX2ZiVDdwSlN6ZXBPYm5uX3h4eG84UHVYc2FFdGJtdmhvNFpIRmxkblNjYjNMMEhJbV9SUG5zUHlFeUwwM1VuTWJtT3hzQ0d3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPX0EycGxDaGFfdUd0ODVhLTJBcnBzaGxpbDJSVm9NME91MVpiZFFqbTFCcEttRGFGRHFpTG16SFFYZHBRcTQxeEN3bW9IM3dsZXB4U3lhZE5xbWdHZjVhVThpWnZYZU1iU2FNWHJGSWNMRmE4bVpfdHpWQ0Nwd0dicldSTlZpVVNHb3pJS192Vmk2UEU3U3plQmhWZXI?oc=5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46141.36355324074</v>
+        <v>46141.45305555555</v>
       </c>
     </row>
     <row r="24">
@@ -1695,27 +1695,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Footage appears to show person being arrested in London after Golders Green stabbing - Sky News</t>
+          <t>‘Particularly badly exposed’: How the Iran war is hitting the UK - Al Jazeera</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Footage appears to show person being arrested in London after Golders Green stabbing - Sky News</t>
+          <t>‘Particularly badly exposed’: How the Iran war is hitting the UK - Al Jazeera</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:59:39 GMT</t>
+          <t>Wed, 29 Apr 2026 08:27:32 GMT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPVFlwcFBZallGZzJVVjVmeWxtMUt4cE44SkxKYTFfbUlOZUQyUG9mSTVmUmlzZm5vVXBWSG9USDJFb1J0LVJScjdnRnJMb2FSMmNLMnpXbnJBMzJQWlJRaHBXbXZMZEJUMzJaVnBSaGJ4eEx2Nm5Od1VGMVhETUxreFJocTRQTlhrdWhTUlRKZXNuR3lXUlV5aTY0c2lNUEVUZ1dkMEg0SFBPREN0b1IzOFplQ3NJanN4MDI1Tw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPdUZPaDc2Q1JIR2hhZVduQzZvd3JKT0xPZGFtOFlybjloQXNMZTJVRk8yZ09BZUE1b2NNRGczamxid2xPM3VYTWV0T2t3WmtmeVZzS0xBSVpVMlBpVzUwNTFtbzhRb3AybXJIQTJ2R1I5RFloSlBHaE5nMDBMaFptUNIBhgFBVV95cUxNdUFuOFFEem04SHhKdGZHLXBJYXRMVzk5Q3dZbnVyZjMwdm11X0E0SGVhcjhYdkNJRldfbGxESURqSnNmUHBwQ2NfbW9ic3dnQnYxeWd6ek5zcDBuM0EwcnBZeW1OcVl3UThKdExNS1FLYXQ1U29uWWVHeUF2UnVuSWM2V2dxUQ?oc=5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46141.49975694445</v>
+        <v>46141.3524537037</v>
       </c>
     </row>
     <row r="25">
@@ -1750,27 +1750,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fourth man arrested after 'stabbing' at Oxford park - Oxford Mail</t>
+          <t>Support staff at schools in 2 London boroughs to strike in pay row - My London</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fourth man arrested after 'stabbing' at Oxford park - Oxford Mail</t>
+          <t>Support staff at schools in 2 London boroughs to strike in pay row - My London</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:58:00 GMT</t>
+          <t>Wed, 29 Apr 2026 07:09:43 GMT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPaUI1MW81X2g2ZDEyeHpzajNkOE1WV0c4Vk10dnRFak1ENWNDRFFXWDVMdUI5VTI3TTI5S29fbHZCV01jSVNUa0xhZmladzFfcWt3VS04V2JSM2RHSjExRjRmQ2FOWnp2dkRDcU41LVk0d3MyMHZYU1hSRm4zOUo0YlJGWlB5aVNhUEx0TDM0V2F6V0Zta2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxORTdHeHF1Sk5EU2pUazRxSS1FOGNKSWNHSUZoSGlTbmNEdG9UQVJNUllqU0dMb0xCOXVrZzQ0RjdOeWI5em5waElrZ194SXh2QnNPcGxMeXN1UFpsZkFCT2Z2SWc5TXVaTkc5aTZ1elItS3E3WlhPaDVlVHB2dC1kdTBRUTBSaVZPNHBNTEJaaXRtQdIBlwFBVV95cUxOaDEwTlRPQjdoMGVFWV9wVURCeDBDZi1kZWVaa3EySVdDemIzajRFcEtha3RqRm9OM0FyaUVPWDlpaUtTNHlVNlJzaDhHRnJSSDBBNlZ3MVFIb0VBU0stN1hEZE83a2NEWjVZM3dYVTRQS2Y5dFRZMkRnQnhORUpsRElDVWpLcUNaOXBtQXVtdjkyQkMzc2lZ?oc=5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1794,38 +1794,38 @@
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46141.45694444444</v>
+        <v>46141.29841435186</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Appeal launched after violent park altercation leaves man stabbed - London Now</t>
+          <t>Bandiere d'Israele e urla di "schifo": scintille in consiglio sul 25 aprile. "Ebrei esclusi, non accadeva dal 1938" - MilanoToday</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Appeal launched after violent park altercation leaves man stabbed - London Now</t>
+          <t>Israeli flags and shouts of "disgust": sparks in the council on April 25th. "Jews excluded, this hasn't happened since 1938" - MilanoToday</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:52:24 GMT</t>
+          <t>Wed, 29 Apr 2026 09:58:16 GMT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPX0EycGxDaGFfdUd0ODVhLTJBcnBzaGxpbDJSVm9NME91MVpiZFFqbTFCcEttRGFGRHFpTG16SFFYZHBRcTQxeEN3bW9IM3dsZXB4U3lhZE5xbWdHZjVhVThpWnZYZU1iU2FNWHJGSWNMRmE4bVpfdHpWQ0Nwd0dicldSTlZpVVNHb3pJS192Vmk2UEU3U3plQmhWZXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOR0VfRG1nTDEzQ3FtanNyaU4xUGd1aTdFR0EtUE9XaUxBYmN1Snh6S2hoTmpUS1hNZ3ItRHRqZzJwelR1SEIxMnFfSXBXQXFpODAzbksyNXFIZnFORFp6TWpKSTA2d3VLN1dBWXgzcEt4blYxNWZRa0VsSzEwN3lWcWNobWx4R19odUNkeHRXOA?oc=5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1835,52 +1835,52 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46141.45305555555</v>
+        <v>46141.41546296296</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>‘Particularly badly exposed’: How the Iran war is hitting the UK - Al Jazeera</t>
+          <t>Sciopero alla Fluid-o-Tech contro il licenziamento di Gianfranco, operato al ginocchio - Il Giorno</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>‘Particularly badly exposed’: How the Iran war is hitting the UK - Al Jazeera</t>
+          <t>Strike at Fluid-o-Tech against the dismissal of Gianfranco, who underwent knee surgery - Il Giorno</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 08:27:32 GMT</t>
+          <t>Wed, 29 Apr 2026 11:31:55 GMT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPdUZPaDc2Q1JIR2hhZVduQzZvd3JKT0xPZGFtOFlybjloQXNMZTJVRk8yZ09BZUE1b2NNRGczamxid2xPM3VYTWV0T2t3WmtmeVZzS0xBSVpVMlBpVzUwNTFtbzhRb3AybXJIQTJ2R1I5RFloSlBHaE5nMDBMaFptUNIBhgFBVV95cUxNdUFuOFFEem04SHhKdGZHLXBJYXRMVzk5Q3dZbnVyZjMwdm11X0E0SGVhcjhYdkNJRldfbGxESURqSnNmUHBwQ2NfbW9ic3dnQnYxeWd6ek5zcDBuM0EwcnBZeW1OcVl3UThKdExNS1FLYXQ1U29uWWVHeUF2UnVuSWM2V2dxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBkYmpTaUtZRzJOT2dvZmpkUlRCZHplbnVCOVVfOUFyNEN5bFlRMUZaR2JkM3dHeUY0NG92cS1wTUlQT291Ulpzcl9WclBCUEdoNWp1Rk5LenJkSy11Q2RnNEo1bE8zNFpZNTRZX2JyRjF5U3ZrSW9VUg?oc=5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1890,52 +1890,52 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46141.3524537037</v>
+        <v>46141.48049768519</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Support staff at schools in 2 London boroughs to strike in pay row - My London</t>
+          <t>Primo maggio 2026, cosa fare a Milano? Corteo, sagre, eventi da non perdere - Mentelocale</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Support staff at schools in 2 London boroughs to strike in pay row - My London</t>
+          <t>May 1st 2026, what to do in Milan? Procession, festivals, events not to be missed - Mentelocale</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:09:43 GMT</t>
+          <t>Wed, 29 Apr 2026 12:00:29 GMT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxORTdHeHF1Sk5EU2pUazRxSS1FOGNKSWNHSUZoSGlTbmNEdG9UQVJNUllqU0dMb0xCOXVrZzQ0RjdOeWI5em5waElrZ194SXh2QnNPcGxMeXN1UFpsZkFCT2Z2SWc5TXVaTkc5aTZ1elItS3E3WlhPaDVlVHB2dC1kdTBRUTBSaVZPNHBNTEJaaXRtQdIBlwFBVV95cUxOaDEwTlRPQjdoMGVFWV9wVURCeDBDZi1kZWVaa3EySVdDemIzajRFcEtha3RqRm9OM0FyaUVPWDlpaUtTNHlVNlJzaDhHRnJSSDBBNlZ3MVFIb0VBU0stN1hEZE83a2NEWjVZM3dYVTRQS2Y5dFRZMkRnQnhORUpsRElDVWpLcUNaOXBtQXVtdjkyQkMzc2lZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQS1BiR3paQlFRY2dNZFhYTHp0S3BwWjIxT2YyMjgwZGZnMmNONkdXa2ItUktveS16SVVneDFSSU9qbjhHSEJ3SnBlYXEyaC1VZm5BVERYSHlCcjZPNElOMjc5bTJHbDB6amFXWUZKLXdPdHJjaFdFbmxPYk1NZDRNOVNGLTZGeV92XzFkaEZpTTZxaW0zYnRrRVVmUlc3a2wwWERPYU92NFJKSUY5b1JzU0tpMzdQUFE?oc=5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1945,21 +1945,21 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46141.29841435186</v>
+        <v>46141.50033564815</v>
       </c>
     </row>
     <row r="29">
@@ -1975,22 +1975,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bandiere d'Israele e urla di "schifo": scintille in consiglio sul 25 aprile. "Ebrei esclusi, non accadeva dal 1938" - MilanoToday</t>
+          <t>Brigata ebraica Milano, non rinunceremo al corteo con le nostre bandiere Archivi - EspansioneTv</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Israeli flags and shouts of "disgust": sparks in the council on April 25th. "Jews excluded, this hasn't happened since 1938" - MilanoToday</t>
+          <t>Milan Jewish Brigade, we will not give up the procession with our flags Archives - EspansioneTv</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 09:58:16 GMT</t>
+          <t>Wed, 29 Apr 2026 09:25:12 GMT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOR0VfRG1nTDEzQ3FtanNyaU4xUGd1aTdFR0EtUE9XaUxBYmN1Snh6S2hoTmpUS1hNZ3ItRHRqZzJwelR1SEIxMnFfSXBXQXFpODAzbksyNXFIZnFORFp6TWpKSTA2d3VLN1dBWXgzcEt4blYxNWZRa0VsSzEwN3lWcWNobWx4R19odUNkeHRXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxORzNwbTVyT1psVlROMHBoYUliYUZoc1JZUXNiUnZ3a092bXBGdnlwQmRxQXg1VE5JZmJoeFJhR19qdXpUQ1hNcElfMUFDVmdUb3JRemhxdUJIMXVjMkVJSmlUb280eU14a0ZFanQya0M2ZlVxTUhwN0E1cWZheTFnYlpwTl9WbW5tb3ZVN3ppTUlwYzZvaktHQ0Q5QUp2Qm55bUdHOTcxQQ?oc=5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46141.41546296296</v>
+        <v>46141.3925</v>
       </c>
     </row>
     <row r="30">
@@ -2030,22 +2030,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sciopero alla Fluid-o-Tech contro il licenziamento di Gianfranco, operato al ginocchio - Il Giorno</t>
+          <t>Domani sciopero in Piazza Affari, presidio fino alle 15 - Bresciaoggi</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Strike at Fluid-o-Tech against the dismissal of Gianfranco, who underwent knee surgery - Il Giorno</t>
+          <t>Strike tomorrow in Piazza Affari, protest until 3pm - Bresciaoggi</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:31:55 GMT</t>
+          <t>Wed, 29 Apr 2026 09:09:35 GMT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBkYmpTaUtZRzJOT2dvZmpkUlRCZHplbnVCOVVfOUFyNEN5bFlRMUZaR2JkM3dHeUY0NG92cS1wTUlQT291Ulpzcl9WclBCUEdoNWp1Rk5LenJkSy11Q2RnNEo1bE8zNFpZNTRZX2JyRjF5U3ZrSW9VUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNaS1oS0ZaVU9jUHlWUVQyNDA3SjdEa3ZZQThMeXdaNzluOUJHUlNpVEwzM19nWkhPMkg5Q29pZ29kMkxRWWU2YkpIdXpjQmJ2THBudkk1S3RSd3F6aU1rYjZsTmRUd1R0M0plbUlVTUhFMXpvdXNhZWVOcjg5TXZsUnNnTDBaVDBSME5tdmxwcEIzREFNcWc3bTdTM2dDVW5CSzYtd1M5QnBZUkJGVDBEb9IBsAFBVV95cUxNaS1oS0ZaVU9jUHlWUVQyNDA3SjdEa3ZZQThMeXdaNzluOUJHUlNpVEwzM19nWkhPMkg5Q29pZ29kMkxRWWU2YkpIdXpjQmJ2THBudkk1S3RSd3F6aU1rYjZsTmRUd1R0M0plbUlVTUhFMXpvdXNhZWVOcjg5TXZsUnNnTDBaVDBSME5tdmxwcEIzREFNcWc3bTdTM2dDVW5CSzYtd1M5QnBZUkJGVDBEbw?oc=5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46141.48049768519</v>
+        <v>46141.38165509259</v>
       </c>
     </row>
     <row r="31">
@@ -2085,22 +2085,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Primo maggio 2026, cosa fare a Milano? Corteo, sagre, eventi da non perdere - Mentelocale</t>
+          <t>Milano, stacca manifesti della commemorazione di Ramelli: picchiato dal branco e lasciato a terra - Il Giorno</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>May 1st 2026, what to do in Milan? Procession, festivals, events not to be missed - Mentelocale</t>
+          <t>Milan, takes down posters commemorating Ramelli: beaten by the pack and left on the ground - Il Giorno</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 12:00:29 GMT</t>
+          <t>Wed, 29 Apr 2026 13:07:30 GMT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQS1BiR3paQlFRY2dNZFhYTHp0S3BwWjIxT2YyMjgwZGZnMmNONkdXa2ItUktveS16SVVneDFSSU9qbjhHSEJ3SnBlYXEyaC1VZm5BVERYSHlCcjZPNElOMjc5bTJHbDB6amFXWUZKLXdPdHJjaFdFbmxPYk1NZDRNOVNGLTZGeV92XzFkaEZpTTZxaW0zYnRrRVVmUlc3a2wwWERPYU92NFJKSUY5b1JzU0tpMzdQUFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNM0tWdmYwS0JWUFRzalBFc0ZaM2lqbWZGQ19nVmU5dGdkeTlOaWpla0MybGZXclpEcmxCaWIxTThKWUxhakp6OEJVVWY2bkFJT3VOYlhpOTVvUDNyalc3dzB1bVhfZzFqdUJlaW5PS3hDbTFBNXpFVkljSW9seHdRZU1PYUxoUUF4V2c?oc=5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46141.50033564815</v>
+        <v>46141.546875</v>
       </c>
     </row>
     <row r="32">
@@ -2140,22 +2140,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brigata ebraica Milano, non rinunceremo al corteo con le nostre bandiere Archivi - EspansioneTv</t>
+          <t>Il 25 aprile e il ruolo dell'Anpi che apre allo squadrismo palestinese mentre il Fatto lancia l'operazione-oblio (grazia a Minetti) post Liberazione - Il Riformista</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Milan Jewish Brigade, we will not give up the procession with our flags Archives - EspansioneTv</t>
+          <t>April 25th and the role of the Anpi which opens up to Palestinian squadrism while Il Fatto launches the post-Liberation oblivion operation (thanks to Minetti) - Il Riformista</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 09:25:12 GMT</t>
+          <t>Wed, 29 Apr 2026 11:08:00 GMT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxORzNwbTVyT1psVlROMHBoYUliYUZoc1JZUXNiUnZ3a092bXBGdnlwQmRxQXg1VE5JZmJoeFJhR19qdXpUQ1hNcElfMUFDVmdUb3JRemhxdUJIMXVjMkVJSmlUb280eU14a0ZFanQya0M2ZlVxTUhwN0E1cWZheTFnYlpwTl9WbW5tb3ZVN3ppTUlwYzZvaktHQ0Q5QUp2Qm55bUdHOTcxQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxQLTJQR1A3UVlwbU02VEZLcUR0bDNSZG1hajNoZWxqLXNyOUpoU0Y1R1UxVXVaZzQ5czRBRnFCZXpYQVduVzRFbHhMUE4tYzJMZGVVOERWVmNnZmFmdlJ1NlZEZFp1QVZCLW9KVGhtMS1iUllmLWtOTDZ0WG1mTTFseFFOOGt4S3FELTVlRHVGSVpnRkV1ZTJoWElOeFVJUmFiRnl6Sm5BVFFwRTRrWEZpSHpkcktrMFIwOVRIVGlDRVlpMGZ4QUJVX0JPRGpjLXpkT2MxWWxlMTVqOE1xMmxTd2hNSERyZzhoMi1ZMmtYbHFOTDlYbU9IYmdwdjFQQ241amktQ1lGSUFfT2Zz?oc=5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46141.3925</v>
+        <v>46141.46388888889</v>
       </c>
     </row>
     <row r="33">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Domani sciopero in Piazza Affari, presidio fino alle 15 - Bresciaoggi</t>
+          <t>Milano, quarantenne sorpreso in auto con le dosi di "polvere della scimmia" - Il Giorno</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Strike tomorrow in Piazza Affari, protest until 3pm - Bresciaoggi</t>
+          <t>Milan, forty-year-old caught in car with doses of "monkey powder" - Il Giorno</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 09:09:35 GMT</t>
+          <t>Wed, 29 Apr 2026 12:37:03 GMT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNaS1oS0ZaVU9jUHlWUVQyNDA3SjdEa3ZZQThMeXdaNzluOUJHUlNpVEwzM19nWkhPMkg5Q29pZ29kMkxRWWU2YkpIdXpjQmJ2THBudkk1S3RSd3F6aU1rYjZsTmRUd1R0M0plbUlVTUhFMXpvdXNhZWVOcjg5TXZsUnNnTDBaVDBSME5tdmxwcEIzREFNcWc3bTdTM2dDVW5CSzYtd1M5QnBZUkJGVDBEb9IBsAFBVV95cUxNaS1oS0ZaVU9jUHlWUVQyNDA3SjdEa3ZZQThMeXdaNzluOUJHUlNpVEwzM19nWkhPMkg5Q29pZ29kMkxRWWU2YkpIdXpjQmJ2THBudkk1S3RSd3F6aU1rYjZsTmRUd1R0M0plbUlVTUhFMXpvdXNhZWVOcjg5TXZsUnNnTDBaVDBSME5tdmxwcEIzREFNcWc3bTdTM2dDVW5CSzYtd1M5QnBZUkJGVDBEbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxObWJwZEpiUjIxd2dDQmM4Y0RJZ3pfb25WTlUxdzJpVmZRTXhBck04QkhwYV9DM0VjNnZ2ODNBNXVjb1k1ZEpMWExxZzM2aWtlYUs2bkkwUk1Xa0pxUUJEU3JMbGR2RllwRDQ4Q29tNHhvYjJET2s2QWJpbkkxMklIMHVwZkE2VkZBR3cxUVpUeTZJUDlOODFsV2JlQnRza0dUdWJpdVRmdHd4d2NYOFgxbA?oc=5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46141.38165509259</v>
+        <v>46141.52572916666</v>
       </c>
     </row>
     <row r="34">
@@ -2250,22 +2250,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Milano, stacca manifesti della commemorazione di Ramelli: picchiato dal branco e lasciato a terra - Il Giorno</t>
+          <t>Milano, il Coordinamento per la Pace attacca la Brigata ebraica: "Stato genocida" - malpensa24</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Milan, takes down posters commemorating Ramelli: beaten by the pack and left on the ground - Il Giorno</t>
+          <t>Milan, the Peace Coordination attacks the Jewish Brigade: "genocidal state" - malpensa24</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 13:07:30 GMT</t>
+          <t>Wed, 29 Apr 2026 07:55:00 GMT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNM0tWdmYwS0JWUFRzalBFc0ZaM2lqbWZGQ19nVmU5dGdkeTlOaWpla0MybGZXclpEcmxCaWIxTThKWUxhakp6OEJVVWY2bkFJT3VOYlhpOTVvUDNyalc3dzB1bVhfZzFqdUJlaW5PS3hDbTFBNXpFVkljSW9seHdRZU1PYUxoUUF4V2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9hZEhGazZ2d0NWRVdvZ2hfQXotX2ZoaGpsN1BSUVhMdXlYWjJnTkhROFZXRkpiczM5Tk5EaVhwdDlYTnd0ZjRxWlRqay1FTC1KYU9CQ0FBU3NZY0R0RjNFakg1cDJLRjVz?oc=5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46141.546875</v>
+        <v>46141.32986111111</v>
       </c>
     </row>
     <row r="35">
@@ -2305,22 +2305,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Il 25 aprile e il ruolo dell'Anpi che apre allo squadrismo palestinese mentre il Fatto lancia l'operazione-oblio (grazia a Minetti) post Liberazione - Il Riformista</t>
+          <t>Ramelli, è già alta tensione a Milano: un 33enne aggredito dopo aver cercato di strappare i manifesti - Affaritaliani</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>April 25th and the role of the Anpi which opens up to Palestinian squadrism while Il Fatto launches the post-Liberation oblivion operation (thanks to Minetti) - Il Riformista</t>
+          <t>Ramelli, tension is already high in Milan: a 33-year-old attacked after trying to tear down the posters - Affaritaliani</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:08:00 GMT</t>
+          <t>Wed, 29 Apr 2026 11:09:33 GMT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxQLTJQR1A3UVlwbU02VEZLcUR0bDNSZG1hajNoZWxqLXNyOUpoU0Y1R1UxVXVaZzQ5czRBRnFCZXpYQVduVzRFbHhMUE4tYzJMZGVVOERWVmNnZmFmdlJ1NlZEZFp1QVZCLW9KVGhtMS1iUllmLWtOTDZ0WG1mTTFseFFOOGt4S3FELTVlRHVGSVpnRkV1ZTJoWElOeFVJUmFiRnl6Sm5BVFFwRTRrWEZpSHpkcktrMFIwOVRIVGlDRVlpMGZ4QUJVX0JPRGpjLXpkT2MxWWxlMTVqOE1xMmxTd2hNSERyZzhoMi1ZMmtYbHFOTDlYbU9IYmdwdjFQQ241amktQ1lGSUFfT2Zz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPWnJ0cUVCYktoc1M3enB3bWhNaVVPWlRIZVRESU5TX3BsVHlFcFhWSjlOZUFWLVc4dHBUc3Y5ZVo5d2NnUjVMdUJtYVVUdC1VY21rbkkxTFJCN1p4M0o2UDFaM1NsTmtKdWpDWjRjRzJzLTJJbG9MN0JnNnhURzY2UTVzd2R1YXpTWGF6Vi1HTjNvT0I2dkkyRWxrSzhaUHZ1cl9BQmtVUlA0MkdzNUM1YTlPanlYNzZyUXphbVJqcGw0QS1NY1hWSlVFWmFEbmMtS0RYUUtTZw?oc=5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2344,38 +2344,38 @@
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46141.46388888889</v>
+        <v>46141.46496527778</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>Spain Transport Disruption English</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Cercanias" OR "Renfe" OR "Madrid Metro" OR "Barcelona Metro" OR "Spanish rail" OR "Madrid motorway" OR "A6 motorway") AND ("bomb threat" OR "suspicious package" OR evacuation OR suspension OR closure OR incident OR "public order" OR arrested OR explosive) AND ("Madrid" OR "Barcelona" OR "Las Rozas" OR "Pozuelo")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Milano, quarantenne sorpreso in auto con le dosi di "polvere della scimmia" - Il Giorno</t>
+          <t>Malaga welcomes first direct high-speed train from Madrid on Thursday following four-month suspension - Sur in English</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Milan, forty-year-old caught in car with doses of "monkey powder" - Il Giorno</t>
+          <t>Malaga welcomes first direct high-speed train from Madrid on Thursday following four-month suspension - Sur in English</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 12:37:03 GMT</t>
+          <t>Wed, 29 Apr 2026 13:38:33 GMT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxObWJwZEpiUjIxd2dDQmM4Y0RJZ3pfb25WTlUxdzJpVmZRTXhBck04QkhwYV9DM0VjNnZ2ODNBNXVjb1k1ZEpMWExxZzM2aWtlYUs2bkkwUk1Xa0pxUUJEU3JMbGR2RllwRDQ4Q29tNHhvYjJET2s2QWJpbkkxMklIMHVwZkE2VkZBR3cxUVpUeTZJUDlOODFsV2JlQnRza0dUdWJpdVRmdHd4d2NYOFgxbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPQURnb1ZrMlJSZEpTRjlBTjZ4ZE9Wczk2ajY5bHloYmp5OW40WERIbWVLaDMyX1JLc1VwVFZNWU1NZElReFlOcFZIYnJKQnRwSVB3ekdlelJHcjIyZ0oyLUM2LUVIZ0E5bWdBaWYzdU9laHRXNUtTUGw3S0xZV2QzQjZURFM1ZnZoYS1maUJ0N3EwYWx1S2VMRjlQM3ZRNWE2MEYxT0RzUXJTQ0JL?oc=5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2385,52 +2385,52 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>ES:en</t>
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46141.52572916666</v>
+        <v>46141.5684375</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>Access Disruption Maasmechelen English (fallback)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Maasmechelen" OR "Genk" OR "Hasselt" OR "E314")</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Milano, il Coordinamento per la Pace attacca la Brigata ebraica: "Stato genocida" - malpensa24</t>
+          <t>Morocco - FotMob</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Milan, the Peace Coordination attacks the Jewish Brigade: "genocidal state" - malpensa24</t>
+          <t>Morocco - FotMob</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:55:00 GMT</t>
+          <t>Wed, 29 Apr 2026 11:14:49 GMT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9hZEhGazZ2d0NWRVdvZ2hfQXotX2ZoaGpsN1BSUVhMdXlYWjJnTkhROFZXRkpiczM5Tk5EaVhwdDlYTnd0ZjRxWlRqay1FTC1KYU9CQ0FBU3NZY0R0RjNFakg1cDJLRjVz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6ANBVV95cUxQQ3VBSHJmcFp6ejYyczIzS18zVXdfNDViYzMzeTVCTndhekRVanVXeXpfNm9oRXhfcHplUVVqenhoOGVFLUp1TEszS3dkX2VRUk1NTFhwRkVFVmRLQ2ZoMERKLXExSHdra0ZneERTYzJfaTRqVG9sckVldlVhZG9wTlZybjgxeXBzWWxyLWtMTk1FTHFuWDZfTHRnQmE5LXFyTVVxQ2pGNGk5cFo2ajMtYjNNME1BRWRja1pDTVZ3VHgwa3dTZ3hnS2hBVG1IaVVtRjQzdVJEeHBXQzN5cFVPQzFZaXhuZl9CVlZjSEczS2VuMEd3VXBHYmZwcHBMd1ZQa1hTX1R6WXVXVm5abmc2RFVyZjhwX2JSNEtxZUp6MkQ1ODVVN0FCdzh1MDdjbmdja0J2UmstbEQ3WkJMT0cwV1BFZVVKcWVjaUpiMHgxcjZ5SmFhY0Y2OGtoVVp1V1lHeXhodS12RlMwMEhVdDNrU2Z0cUxHSlFwVEVTME9hRlFCbWdJQkZhYUFmWkxaX1VvcEZlTlRJaERmTUZwMDVXcDhDZzVVb2xjUHAya2xwNFRIcENEQlZKdVdpZUJMclJKUHg0bE53QlRnLTV0U3p6NGR0bGF0TllhS2RZT1dXeHBOX1c3UDh3UA?oc=5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2440,52 +2440,52 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46141.32986111111</v>
+        <v>46141.46862268518</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>Access Disruption Maasmechelen English (fallback)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Maasmechelen" OR "Genk" OR "Hasselt" OR "E314")</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ramelli, è già alta tensione a Milano: un 33enne aggredito dopo aver cercato di strappare i manifesti - Affaritaliani</t>
+          <t>Beşiktaş Eye Move For Arokodare - LEADERSHIP Newspapers</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ramelli, tension is already high in Milan: a 33-year-old attacked after trying to tear down the posters - Affaritaliani</t>
+          <t>Beşiktaş Eye Move For Arokodare - LEADERSHIP Newspapers</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:09:33 GMT</t>
+          <t>Wed, 29 Apr 2026 10:50:38 GMT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPWnJ0cUVCYktoc1M3enB3bWhNaVVPWlRIZVRESU5TX3BsVHlFcFhWSjlOZUFWLVc4dHBUc3Y5ZVo5d2NnUjVMdUJtYVVUdC1VY21rbkkxTFJCN1p4M0o2UDFaM1NsTmtKdWpDWjRjRzJzLTJJbG9MN0JnNnhURzY2UTVzd2R1YXpTWGF6Vi1HTjNvT0I2dkkyRWxrSzhaUHZ1cl9BQmtVUlA0MkdzNUM1YTlPanlYNzZyUXphbVJqcGw0QS1NY1hWSlVFWmFEbmMtS0RYUUtTZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBrRl9ORlNoU0F1dnZpUURyU2R2aVZuQnRCRk93ZnFXRjl5b0R2T1R0V0VUUEY2R3NDX1FOb1ViUlFkeDBoMndFelg2LUFvcWlyX2MyUFY2MkdYaTZDZDJ1WWd1Q0w?oc=5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2495,21 +2495,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46141.46496527778</v>
+        <v>46141.45182870371</v>
       </c>
     </row>
     <row r="39">
@@ -2525,22 +2525,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Morocco - FotMob</t>
+          <t>Braga vs Freiburg prediction and betting tips 30 April 2026 - Dailysports</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Morocco - FotMob</t>
+          <t>Braga vs Freiburg prediction and betting tips 30 April 2026 - Dailysports</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:14:49 GMT</t>
+          <t>Wed, 29 Apr 2026 11:33:42 GMT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6ANBVV95cUxQQ3VBSHJmcFp6ejYyczIzS18zVXdfNDViYzMzeTVCTndhekRVanVXeXpfNm9oRXhfcHplUVVqenhoOGVFLUp1TEszS3dkX2VRUk1NTFhwRkVFVmRLQ2ZoMERKLXExSHdra0ZneERTYzJfaTRqVG9sckVldlVhZG9wTlZybjgxeXBzWWxyLWtMTk1FTHFuWDZfTHRnQmE5LXFyTVVxQ2pGNGk5cFo2ajMtYjNNME1BRWRja1pDTVZ3VHgwa3dTZ3hnS2hBVG1IaVVtRjQzdVJEeHBXQzN5cFVPQzFZaXhuZl9CVlZjSEczS2VuMEd3VXBHYmZwcHBMd1ZQa1hTX1R6WXVXVm5abmc2RFVyZjhwX2JSNEtxZUp6MkQ1ODVVN0FCdzh1MDdjbmdja0J2UmstbEQ3WkJMT0cwV1BFZVVKcWVjaUpiMHgxcjZ5SmFhY0Y2OGtoVVp1V1lHeXhodS12RlMwMEhVdDNrU2Z0cUxHSlFwVEVTME9hRlFCbWdJQkZhYUFmWkxaX1VvcEZlTlRJaERmTUZwMDVXcDhDZzVVb2xjUHAya2xwNFRIcENEQlZKdVdpZUJMclJKUHg0bE53QlRnLTV0U3p6NGR0bGF0TllhS2RZT1dXeHBOX1c3UDh3UA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPdGJmX2V2Q2NQWDRHMWVQQnUwTWhDQzhpSGhUeGlzbzgzUHFnT0sxN0s4TWFib1dLTmV4eEd2ZHkxTmprSUpTakd3cHBZWGJuOVpKZ1pNZDMyS1FOelVQQ1hVZDVyc3N5dkdJcV84NmxRekhfWmZaRlBTRU5TTmc0bzFxY0xFMEw3SDlwZEE4YU9RQ3JGSUw5NGs1VmVZNDZ6?oc=5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2564,38 +2564,38 @@
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46141.46862268518</v>
+        <v>46141.48173611111</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Access Disruption Maasmechelen English (fallback)</t>
+          <t>Access Disruption Wertheim English (fallback)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Genk" OR "Hasselt" OR "E314")</t>
+          <t>("Wertheim" OR "A3 autobahn" OR "Würzburg" OR "Aschaffenburg")</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Volvo's falling sales mount pressure on Belgian factory - The Brussels Times</t>
+          <t>Afghan knifeman attacks multiple people at German train station before being overpowered - MSN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Volvo's falling sales mount pressure on Belgian factory - The Brussels Times</t>
+          <t>Afghan knifeman attacks multiple people at German train station before being overpowered - MSN</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 13:19:36 GMT</t>
+          <t>Wed, 29 Apr 2026 11:58:28 GMT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPeEJtbERGb1JYNGJVaDh6Z1kxdUVoQ1RaTGU5WWg1VmV4Qzh1dzBjNmpoY2ZLZ1dvbGJ3b0lWMTZoNEFGT2dnWEhxTFFUOVU0VFI2NmcwemZJT1gtTFI0LVNqRUl6Skppb2xDMUVJRkNMM1R6cWtJc3BRWkRSZU5TZFItcUR3THM0ZjJnMTJpMk5IUmItOU5ndmRObkgyUGJsSllB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwNBVV95cUxPclJYUXNJZ0cwSXVDalBwbDljVkxvY0hTcFV1LXRxSG8wREE4YWxYdlNoSWxfQ21sZzlXMkdfY2JNZWVBNGIydFU1ajJxTHZuM0YzczBlX2dlVTJ3MmcxMnE0ZERUMHo3ZmNBcEN2d1pyNVlZRU94dmo4amNYdU94Smk4ZWx5M0YxWkJzV2hoaHF4RUJSakF5QnB6T0tyRWc5RFNVVURyV1Zrc3NjSjNpS2tBVkZsVXRkSUpCbG8xRmNRY3p2WER3RzhmdzRTMElBUjdTdFhGamRUYWs3RG1iZXJqZ2tKNnlJbFdrLUNFZXFlLVlHM3dnOTVEMkI4NS16VGxKNlFQYXhOSTBtZmRjUnd0TTMzNW1kR0VidThWVVd1Ymk5MDg3Tk9sdFZVS21tR2NuZTI3TXJwVVpEblM5SnluV3EwYTNzenhOT0hoalF2MUdKaUtVSGN2amRfQ21YRUdhWFV0eGVhcXBvenV5RHhRMlVpVHBXY2RUSHF1amJoQThRR0ZB?oc=5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2619,38 +2619,38 @@
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46141.55527777778</v>
+        <v>46141.49893518518</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Access Disruption Maasmechelen English (fallback)</t>
+          <t>Access Disruption Wertheim English (fallback)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Genk" OR "Hasselt" OR "E314")</t>
+          <t>("Wertheim" OR "A3 autobahn" OR "Würzburg" OR "Aschaffenburg")</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Beşiktaş Eye Move For Arokodare - LEADERSHIP Newspapers</t>
+          <t>Larry M. Wertheim - Star Tribune</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Beşiktaş Eye Move For Arokodare - LEADERSHIP Newspapers</t>
+          <t>Larry M. Wertheim - Star Tribune</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:50:38 GMT</t>
+          <t>Wed, 29 Apr 2026 07:03:51 GMT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBrRl9ORlNoU0F1dnZpUURyU2R2aVZuQnRCRk93ZnFXRjl5b0R2T1R0V0VUUEY2R3NDX1FOb1ViUlFkeDBoMndFelg2LUFvcWlyX2MyUFY2MkdYaTZDZDJ1WWd1Q0w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9OWE1UMEZfX3dHWnZlNjVkbWVoeksxSHQxeTkwWFFrM0J2TzN3VWx3by1sdVhONEI4b3VqYk5GMW53RW1MUERiU1c2YnF4TUlPdG9SS1lBY0ozTHNrZU52aGhDY190ZUJEYTVIWDF3bzlzU3ZaQTdkMw?oc=5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2674,38 +2674,38 @@
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46141.45182870371</v>
+        <v>46141.29434027777</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Access Disruption Maasmechelen English (fallback)</t>
+          <t>Access Disruption Wertheim English (fallback)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Genk" OR "Hasselt" OR "E314")</t>
+          <t>("Wertheim" OR "A3 autobahn" OR "Würzburg" OR "Aschaffenburg")</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Braga vs Freiburg prediction and betting tips 30 April 2026 - Dailysports</t>
+          <t>Stars who smoke—and the reactions they sparked - MSN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Braga vs Freiburg prediction and betting tips 30 April 2026 - Dailysports</t>
+          <t>Stars who smoke—and the reactions they sparked - MSN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:33:42 GMT</t>
+          <t>Wed, 29 Apr 2026 07:33:37 GMT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPdGJmX2V2Q2NQWDRHMWVQQnUwTWhDQzhpSGhUeGlzbzgzUHFnT0sxN0s4TWFib1dLTmV4eEd2ZHkxTmprSUpTakd3cHBZWGJuOVpKZ1pNZDMyS1FOelVQQ1hVZDVyc3N5dkdJcV84NmxRekhfWmZaRlBTRU5TTmc0bzFxY0xFMEw3SDlwZEE4YU9RQ3JGSUw5NGs1VmVZNDZ6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNYnNJLVMxdjZzbUZYaXcyRjBqb1dSNkd1aVp2VzlpaTJCdVlnZVF0bE0zT2hxLXZQeFZYUU1Bc2l6Q0lMQi1QSTNLT0x5RmFzSmlSQTJsWVQzQmNpLWdVc2tPWk1NMTFnY2VfNk9rdkpFNWJhV2JITnhuTktoVk01NHFVRDcyS0lkT0pKRXpCMDJycjRjc0JaODI4eUI?oc=5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2729,38 +2729,38 @@
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46141.48173611111</v>
+        <v>46141.31501157407</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Access Disruption Wertheim English (fallback)</t>
+          <t>Access Disruption Ingolstadt German</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Wertheim" OR "A3 autobahn" OR "Würzburg" OR "Aschaffenburg")</t>
+          <t>("Ingolstadt" OR "A9" OR "A8" OR "B9") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz) AND -Audi AND -Auto AND -Wetter AND -Sport</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Larry M. Wertheim - Star Tribune</t>
+          <t>Heftiger A9-Unfall bei Schweitenkirchen: 23-Jähriger überschlägt sich nach Crash - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Larry M. Wertheim - Star Tribune</t>
+          <t>Violent A9 accident near Schweitenkirchen: 23-year-old rolls over after crash - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:03:51 GMT</t>
+          <t>Wed, 29 Apr 2026 13:28:11 GMT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9OWE1UMEZfX3dHWnZlNjVkbWVoeksxSHQxeTkwWFFrM0J2TzN3VWx3by1sdVhONEI4b3VqYk5GMW53RW1MUERiU1c2YnF4TUlPdG9SS1lBY0ozTHNrZU52aGhDY190ZUJEYTVIWDF3bzlzU3ZaQTdkMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9CRlpfdmJHTkxyMmtPNVk0S2hEQ2F6UUNRazBTZ21vMzJTTlRnUzBzTHlURkNnQ1hZaHJ6SmpSUkRiMmFGaVVfLW1aVXdnSXEwSzFRQ2dkTkhFVTJpZDhjaUI5eTdQZGtHT2ptYQ?oc=5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2770,21 +2770,21 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46141.29434027777</v>
+        <v>46141.56123842593</v>
       </c>
     </row>
     <row r="44">
@@ -2800,22 +2800,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Heftiger A9-Unfall bei Schweitenkirchen: 23-Jähriger überschlägt sich nach Crash - Pfaffenhofen Today</t>
+          <t>Auffahrunfall auf A8 bei Leonberg führt zu Zeugensuche - AsatuNews.co.id</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Violent A9 accident near Schweitenkirchen: 23-year-old rolls over after crash - Pfaffenhofen Today</t>
+          <t>Rear-end collision on A8 near Leonberg leads to search for witnesses - AsatuNews.co.id</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 13:28:11 GMT</t>
+          <t>Wed, 29 Apr 2026 11:58:41 GMT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9CRlpfdmJHTkxyMmtPNVk0S2hEQ2F6UUNRazBTZ21vMzJTTlRnUzBzTHlURkNnQ1hZaHJ6SmpSUkRiMmFGaVVfLW1aVXdnSXEwSzFRQ2dkTkhFVTJpZDhjaUI5eTdQZGtHT2ptYQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE04SGV5SWFVcWllYWVpcDluNHhaLTlJSU5Jamw5Q192YklxWnByNFp6RDFXRzBzYUE1dnZvUjVvTnJWWjdPUlpKLVFmTWloRjJHbmFkb1FBQjF1QjU0NktYT1pVUWJkTzNPWGtuSk0xZG0zZw?oc=5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46141.56123842593</v>
+        <v>46141.49908564815</v>
       </c>
     </row>
     <row r="45">
@@ -2855,22 +2855,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>News of the day vom 29.04.2026: Verheerender Wohnungsbrand in Nürnberg Reichelsdorf - eine Person verstorben - Franken Fernsehen</t>
+          <t>Wegen Unfall auf A9: Sperrung zwischen Siders-Ost und Siders-West - Unfallmeldungen.ch</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>News of the day from April 29, 2026: Devastating apartment fire in Nuremberg Reichelsdorf - one person died - Franken Fernsehen</t>
+          <t>Due to an accident on the A9: closure between Siders-East and Siders-West - accident reports.ch</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:13:37 GMT</t>
+          <t>Wed, 29 Apr 2026 10:39:16 GMT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNclRsZ045YVdyWk9BY2g3cll0ZExmOURkZnpKYnRGWmV5Y05oVnJVSHZyS0FMVkRZenFLeThfMDdHWUJEcUJzRFhLR05YVF9nOWJwYVlBTEpRR1gyaGxqNjFKT3NTeEVpdWM5U2t5YUN4eFluS0JoekNhXzV1YlFPdTlXTEFrY29yTFZ3dmJmVmd5ZXhHbVVMMUZyWURyZUwzak1ySl93UkRXUjhoZ3Z4U3N3LVdaTmlIcTRLSkc5Rkd2bnVmS0R4V2N0anh0R3JXeFl4eHF1dUJDQ00yN2loRGpKcUFJV2RZY2Zn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNaDdvdlU1NHFzOVd1VUZDSGlNUmhYQ2pDYXRpeDVJSDBsQmZXY2tfUlZsNWtjY3BvTHJadnZaTVQwNVE4X2xGV2RoQ24yVkx3cG5XckhNblhZZExhMVVEX3JhbFBuS1NiU2NqYnVfVk5ZVWdERW81SnZSeWFvV3lLY1VkWHZGODhNT01QNkZ3R2NscjhnOWh0aEdzaVM0eTRHemNpN3R3?oc=5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46141.46778935185</v>
+        <v>46141.44393518518</v>
       </c>
     </row>
     <row r="46">
@@ -2910,22 +2910,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Auffahrunfall auf A8 bei Leonberg führt zu Zeugensuche - AsatuNews.co.id</t>
+          <t>Wegen Unfall auf A2: Verkehrsbehinderung zwischen Beckenried und Buochs - Unfallmeldungen.ch</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Rear-end collision on A8 near Leonberg leads to search for witnesses - AsatuNews.co.id</t>
+          <t>Due to an accident on the A2: traffic obstruction between Beckenried and Buochs ​​- accident reports.ch</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:58:41 GMT</t>
+          <t>Wed, 29 Apr 2026 10:39:06 GMT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE04SGV5SWFVcWllYWVpcDluNHhaLTlJSU5Jamw5Q192YklxWnByNFp6RDFXRzBzYUE1dnZvUjVvTnJWWjdPUlpKLVFmTWloRjJHbmFkb1FBQjF1QjU0NktYT1pVUWJkTzNPWGtuSk0xZG0zZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNaVNQeWVUYkdyQ2xxOVRmc2xqN0NZalNOa082OVA2UjNxbzJsMlNkbU92RUN4QUVOY2R6SVZ6SENMQ2tSeHBRTXFMYm8wYVpyTl91TGxZYXZtdUlQTFAwLUplZm1uSzJpdFdsdXppMkhKNjg0ZkRiQ2R6U0o1M2x4MjVQaEgzUXBrX295NHRhWm1XcXRmNFpzQzJVUWNkV2tzSXc2aS05M2llUktRWnc?oc=5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2949,38 +2949,38 @@
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46141.49908564815</v>
+        <v>46141.44381944444</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Access Disruption Ingolstadt German</t>
+          <t>Access Disruption Fidenza Italian</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Ingolstadt" OR "A9" OR "A8" OR "B9") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz) AND -Audi AND -Auto AND -Wetter AND -Sport</t>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wegen Unfall auf A9: Sperrung zwischen Siders-Ost und Siders-West - Unfallmeldungen.ch</t>
+          <t>Incidente oggi in A13, autostrada nel caos per un camion ribaltato: tratto chiuso per ore e code - Il Resto del Carlino</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Due to an accident on the A9: closure between Siders-East and Siders-West - accident reports.ch</t>
+          <t>Accident today on the A13, highway in chaos due to an overturned truck: section closed for hours and queues - Il Resto del Carlino</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:39:16 GMT</t>
+          <t>Wed, 29 Apr 2026 10:57:48 GMT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNaDdvdlU1NHFzOVd1VUZDSGlNUmhYQ2pDYXRpeDVJSDBsQmZXY2tfUlZsNWtjY3BvTHJadnZaTVQwNVE4X2xGV2RoQ24yVkx3cG5XckhNblhZZExhMVVEX3JhbFBuS1NiU2NqYnVfVk5ZVWdERW81SnZSeWFvV3lLY1VkWHZGODhNT01QNkZ3R2NscjhnOWh0aEdzaVM0eTRHemNpN3R3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQTmZqWkZKQXlfTF9JbldkRXY4bUphTHB5dktsdDBqbk0yRTdyek8wM1JuSnhlM2xtYUZaNE9iSy1HN0ZqbWloVlRvV3VqZFY3VWJ4UWJ1b0JTVnV2RDVwVklMMW1tZVJqQXp1c3ZjMV8xWnQxNWJ1TkR3U1NCWEwxSA?oc=5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2990,52 +2990,52 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46141.44393518518</v>
+        <v>46141.45680555556</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Access Disruption Ingolstadt German</t>
+          <t>Access Disruption Fidenza Italian</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Ingolstadt" OR "A9" OR "A8" OR "B9") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz) AND -Audi AND -Auto AND -Wetter AND -Sport</t>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wegen Unfall auf A2: Verkehrsbehinderung zwischen Beckenried und Buochs - Unfallmeldungen.ch</t>
+          <t>Autostrada A24, chiusura notturna della tratta L’Aquila Ovest-Tornimparte - ConfineLive</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Due to an accident on the A2: traffic obstruction between Beckenried and Buochs ​​- accident reports.ch</t>
+          <t>A24 motorway, night closure of the L'Aquila West-Tornimparte section - ConfineLive</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:39:06 GMT</t>
+          <t>Wed, 29 Apr 2026 09:00:32 GMT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNaVNQeWVUYkdyQ2xxOVRmc2xqN0NZalNOa082OVA2UjNxbzJsMlNkbU92RUN4QUVOY2R6SVZ6SENMQ2tSeHBRTXFMYm8wYVpyTl91TGxZYXZtdUlQTFAwLUplZm1uSzJpdFdsdXppMkhKNjg0ZkRiQ2R6U0o1M2x4MjVQaEgzUXBrX295NHRhWm1XcXRmNFpzQzJVUWNkV2tzSXc2aS05M2llUktRWnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQcUgyNDVTVjhzdUxDOW95VUU5aVdqdk5wNEpULUlELWg1V0tPX29ZUFNfaDI1WUs3ZnBhaTFfNGE0VmNCTkFjYzBUTk1EVU5helBWQjV1UEIwNl9nRmVrQlkzM19uWUl4WWcyQ2FZTXNCSU5PNWRLSDVfajhwMVFseVB1LU1KTGhNVVdDS0xyOVhPUHpheDl2WVNUbUZKM0lK?oc=5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3045,52 +3045,52 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46141.44381944444</v>
+        <v>46141.37537037037</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Access Disruption Ingolstadt English (fallback)</t>
+          <t>Access Disruption Fidenza Italian</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Ingolstadt" OR "A9 autobahn" OR "A8 autobahn")</t>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Viktoria Köln 1904 - FotMob</t>
+          <t>Incidente sull’A13 a Occhiobello: autotreno si ribalta, autostrada chiusa in direzione nord - La Piazza Web</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Victoria Cologne 1904 - PhotoMob</t>
+          <t>Accident on the A13 in Occhiobello: lorry overturns, motorway closed heading north - La Piazza Web</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:23:08 GMT</t>
+          <t>Wed, 29 Apr 2026 07:22:00 GMT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPUWdnTW54d0VmNlNJeUpBdEgxRDJOTWhQeUhETWtSVFlKck1jdmpWWlJ6c2o2YjhsbDlHWVdnZmFOTHNFUTRPZndRVllfYVRXenE0VDBpV3pxN3BtNjZ3dHBMZUoxN1RTcjhETUlNVC1KQmRCX0haNFN6RTRsS0hqa1dnSVkwTjBZU3puQUJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQUUlnZTI5SGI1SHNvTFAyNzBQeE01VWVtUkxWcWVrU3N5clA3UEhUSXJuc18taFdOX3k2QTVrckYyWlBXNjBubTJ2QlRZdWZkV1RWTWxvdkdyaFJRbmF6YzRsTnRHSTcydVp6cEx1RzVTR0E3N3VwV3pKZG5nM1VFekpfT3JoaUt0MFdmdGZRU1dwSGNQNE1oNFNrM0ZJNFFrbmE1NHVnWFZMU0VCNFpvZzhPYUtIQnZOdGt0SmNLTnRKM1ZMY3JYV1N1TTktNkFxTUtB?oc=5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3100,21 +3100,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46141.30773148148</v>
+        <v>46141.30694444444</v>
       </c>
     </row>
     <row r="50">
@@ -3130,22 +3130,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Incidente oggi in A13, autostrada nel caos per un camion ribaltato: tratto chiuso per ore e code - Il Resto del Carlino</t>
+          <t>Incidente A13 oggi: tratto riaperto ma 7 km di coda verso Padova - SICURAUTO.it</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Accident today on the A13, highway in chaos due to an overturned truck: section closed for hours and queues - Il Resto del Carlino</t>
+          <t>A13 accident today: section reopened but 7 km of queue towards Padua - SICURAUTO.it</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:57:48 GMT</t>
+          <t>Wed, 29 Apr 2026 07:45:00 GMT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQTmZqWkZKQXlfTF9JbldkRXY4bUphTHB5dktsdDBqbk0yRTdyek8wM1JuSnhlM2xtYUZaNE9iSy1HN0ZqbWloVlRvV3VqZFY3VWJ4UWJ1b0JTVnV2RDVwVklMMW1tZVJqQXp1c3ZjMV8xWnQxNWJ1TkR3U1NCWEwxSA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVTRGSzY4bW5XYjN4QVdrVHBJdUFXQmhPelBiWHduV2lPTkJVUkY1SlFOMUNFekxuQWUwY3R0WXY2cTRrVmd1Zi1NMGNMZnBkUW5xLTZvOXVvNTk5T0xadHEtdnlHMnB3SmpHc0dsRFlHZG5zYkFhRVBzcG85cDBSN29KOUNUMXpfT0xaMkxlM1I4azJfM1NpTjNRZkVRXzhEOHZUbGtIdWoxZw?oc=5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46141.45680555556</v>
+        <v>46141.32291666666</v>
       </c>
     </row>
     <row r="51">
@@ -3185,22 +3185,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Autostrada A24, chiusura notturna della tratta L’Aquila Ovest-Tornimparte - ConfineLive</t>
+          <t>Incidente sull’autostrada A2 Salerno-Reggio, scontro con auto ribaltata: 4 feriti - Fanpage</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>A24 motorway, night closure of the L'Aquila West-Tornimparte section - ConfineLive</t>
+          <t>Accident on the A2 Salerno-Reggio motorway, collision with overturned car: 4 injured - Fanpage</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 09:00:32 GMT</t>
+          <t>Wed, 29 Apr 2026 12:34:33 GMT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQcUgyNDVTVjhzdUxDOW95VUU5aVdqdk5wNEpULUlELWg1V0tPX29ZUFNfaDI1WUs3ZnBhaTFfNGE0VmNCTkFjYzBUTk1EVU5helBWQjV1UEIwNl9nRmVrQlkzM19uWUl4WWcyQ2FZTXNCSU5PNWRLSDVfajhwMVFseVB1LU1KTGhNVVdDS0xyOVhPUHpheDl2WVNUbUZKM0lK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPSjlHZGVBeksyakZRRXFUaGRvTFBFTVVlWTE5X2x2QXl2aHFtZGRJM0ItMkNpWlh3RHVQS0lvY2RuelMtTHY5ZkNZVG5NTGpZVWdFSHlQSkpUR2toY0w4bU1NZWk5MVVQR0dCZm9UUzZmb255VnBuLVBoMTY0Y0lMZmpYTnZfaGNzSzJpLTc5RGxSelU5LTdsQ3F2eTBuUTBJbjVkSU54b0gtcUdQcVE?oc=5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46141.37537037037</v>
+        <v>46141.52399305555</v>
       </c>
     </row>
     <row r="52">
@@ -3240,22 +3240,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Incidente sull’A13 a Occhiobello: autotreno si ribalta, autostrada chiusa in direzione nord - La Piazza Web</t>
+          <t>Brennero, stop totale domani: chiusura completa e divieto di transito per i camion - Trans.INFO</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Accident on the A13 in Occhiobello: lorry overturns, motorway closed heading north - La Piazza Web</t>
+          <t>Brenner, total stop tomorrow: complete closure and transit ban for trucks - Trans.INFO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:22:00 GMT</t>
+          <t>Wed, 29 Apr 2026 09:43:13 GMT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQUUlnZTI5SGI1SHNvTFAyNzBQeE01VWVtUkxWcWVrU3N5clA3UEhUSXJuc18taFdOX3k2QTVrckYyWlBXNjBubTJ2QlRZdWZkV1RWTWxvdkdyaFJRbmF6YzRsTnRHSTcydVp6cEx1RzVTR0E3N3VwV3pKZG5nM1VFekpfT3JoaUt0MFdmdGZRU1dwSGNQNE1oNFNrM0ZJNFFrbmE1NHVnWFZMU0VCNFpvZzhPYUtIQnZOdGt0SmNLTnRKM1ZMY3JYV1N1TTktNkFxTUtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOekozb0dVMk5hSTZQNVVRbklEWlBjREF0NVA5ZUdnT01BSXdJZmJ0ZzZCYndyclJ3U2xQMEtpZERsWkYwT3dBcld6aTVsTVBQMG5zMUt3QmdJUVh5X3BROHdUY0ZzT2JyRHFXNGFLaEt5TTZ5dEI5aENJaGw0aGZBS3VWZ2drbTdTM3RTTmFrOHpleVhFeklSV3JVQmh2TzBqQ1FWb1JEeXlXMW9LNWc?oc=5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46141.30694444444</v>
+        <v>46141.40501157408</v>
       </c>
     </row>
     <row r="53">
@@ -3295,22 +3295,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Incidente A13 oggi: tratto riaperto ma 7 km di coda verso Padova - SICURAUTO.it</t>
+          <t>Palermo, incidente con 5 feriti in via Nicoletti: chiuso lo svincolo Sferracavallo dell’A29 - Meridionews</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>A13 accident today: section reopened but 7 km of queue towards Padua - SICURAUTO.it</t>
+          <t>Palermo, accident with 5 injured in via Nicoletti: the Sferracavallo junction of the A29 closed - Meridionews</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:45:00 GMT</t>
+          <t>Wed, 29 Apr 2026 08:12:30 GMT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVTRGSzY4bW5XYjN4QVdrVHBJdUFXQmhPelBiWHduV2lPTkJVUkY1SlFOMUNFekxuQWUwY3R0WXY2cTRrVmd1Zi1NMGNMZnBkUW5xLTZvOXVvNTk5T0xadHEtdnlHMnB3SmpHc0dsRFlHZG5zYkFhRVBzcG85cDBSN29KOUNUMXpfT0xaMkxlM1I4azJfM1NpTjNRZkVRXzhEOHZUbGtIdWoxZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBQdGZPT3BZX05EYnI4Zm0tMXRMM0cteWZJVWl6azQteDI4X3ZaRDZDcDFYWnV0eUx0SnN0Nmo0WmlkbWZrYTJCRWZaRHY5SmNPbVJTYW03YVVULTlqNHE0cWlDQWp5Zw?oc=5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3334,116 +3334,6 @@
         </is>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46141.32291666666</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Access Disruption Fidenza Italian</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Incidente sull’autostrada A2 Salerno-Reggio, scontro con auto ribaltata: 4 feriti - Fanpage</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Accident on the A2 Salerno-Reggio motorway, collision with overturned car: 4 injured - Fanpage</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Wed, 29 Apr 2026 12:34:33 GMT</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPSjlHZGVBeksyakZRRXFUaGRvTFBFTVVlWTE5X2x2QXl2aHFtZGRJM0ItMkNpWlh3RHVQS0lvY2RuelMtTHY5ZkNZVG5NTGpZVWdFSHlQSkpUR2toY0w4bU1NZWk5MVVQR0dCZm9UUzZmb255VnBuLVBoMTY0Y0lMZmpYTnZfaGNzSzJpLTc5RGxSelU5LTdsQ3F2eTBuUTBJbjVkSU54b0gtcUdQcVE?oc=5</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K54" s="1" t="n">
-        <v>46141.52399305555</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Access Disruption Fidenza Italian</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Palermo, incidente con 5 feriti in via Nicoletti: chiuso lo svincolo Sferracavallo dell’A29 - Meridionews</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Palermo, accident with 5 injured in via Nicoletti: the Sferracavallo junction of the A29 closed - Meridionews</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Wed, 29 Apr 2026 08:12:30 GMT</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBQdGZPT3BZX05EYnI4Zm0tMXRMM0cteWZJVWl6azQteDI4X3ZaRDZDcDFYWnV0eUx0SnN0Nmo0WmlkbWZrYTJCRWZaRHY5SmNPbVJTYW03YVVULTlqNHE0cWlDQWp5Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K55" s="1" t="n">
         <v>46141.34201388889</v>
       </c>
     </row>
